--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_242_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_242_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
         <v>12</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -904,12 +904,12 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -1531,7 +1531,7 @@
         <v>14</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1727,7 +1727,7 @@
         <v>17</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2122,13 +2122,13 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X21" t="n">
         <v>7</v>
@@ -2514,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2903,16 +2903,16 @@
         <v>2</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
         <v>2</v>
@@ -3102,13 +3102,13 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X26" t="n">
         <v>3</v>
@@ -3827,16 +3827,16 @@
         <v>106</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X30" t="n">
         <v>29</v>
@@ -4488,7 +4488,7 @@
         <v>15</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -5275,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -6784,10 +6784,10 @@
         <v>67</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V48" t="n">
         <v>0</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_242_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_242_EL.xlsx
@@ -674,10 +674,10 @@
         <v>12</v>
       </c>
       <c r="N2" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="O2" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>96.67</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="P3" t="n">
         <v>8</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1543,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -1739,10 +1739,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -2131,14 +2131,14 @@
         <v>2</v>
       </c>
       <c r="X21" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA21" t="n">
@@ -2523,10 +2523,10 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         <v>1</v>
       </c>
       <c r="X25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3839,14 +3839,14 @@
         <v>4</v>
       </c>
       <c r="X30" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="Y30" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>94.4%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4500,14 +4500,14 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Y36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AA36" t="n">
@@ -5284,14 +5284,14 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -6796,14 +6796,14 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="Y48" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="AA48" t="n">
